--- a/IntelliDraft_API_Endpoints.xlsx
+++ b/IntelliDraft_API_Endpoints.xlsx
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1078,26 +1078,26 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Ingestion</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>/api/submit-inputs</t>
+          <t>/api/document/{doc_id}</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Save user inputs onto a parsed document</t>
+          <t>Parsed-document metadata</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>{document_id, ...}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
@@ -1118,7 +1118,7 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>/api/document/{doc_id}</t>
+          <t>/api/document/{doc_id}/status</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Parsed-document metadata</t>
+          <t>Document processing status/index</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1158,26 +1158,26 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
           <t>Ingestion</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>/api/document/{doc_id}/status</t>
+          <t>/api/extract-project-data</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Document processing status/index</t>
+          <t>LLM-extract project fields from documents</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -1187,22 +1187,22 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{document_ids:[...]}</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>200 / 404</t>
+          <t>200 / 404 / 502</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Ingestion</t>
+        <v>15</v>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Generation</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>/api/extract-project-data</t>
+          <t>/api/generate/project/{project_id}</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>LLM-extract project fields from documents</t>
+          <t>Start / resume generation for a project</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1227,37 +1227,37 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>{document_ids:[...]}</t>
+          <t>{document_type}</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>200 / 404 / 502</t>
+          <t>201 / 200 (already) / 404</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
           <t>Generation</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>/api/generate/start</t>
+          <t>/api/generate/{job_id}</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>DEPRECATED — start job from a document_id</t>
+          <t>Job status + sections (client polls this)</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1267,37 +1267,37 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>{document_id, user_inputs}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>200 / 404</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
           <t>Generation</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>/api/generate/project/{project_id}</t>
+          <t>/api/generate/{job_id}/section/{section_id}</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Start / resume generation for a project</t>
+          <t>One section w/ all versions + comments</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1307,47 +1307,47 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>{document_type}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>201 / 200 (already) / 404</t>
+          <t>200 / 404</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
           <t>Generation</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>/api/generate/{job_id}</t>
+          <t>/api/generate/{job_id}/section/{section_id}</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Job status + sections (client polls this)</t>
+          <t>Manual content override → new version</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>opt (attribution)</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{content}</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
@@ -1358,26 +1358,26 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
           <t>Generation</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>/api/generate/{job_id}/section/{section_id}</t>
+          <t>/api/generate/{job_id}/section/{section_id}/comment</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>One section w/ all versions + comments</t>
+          <t>Add an edit-request comment</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1387,47 +1387,47 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{comment_text, comment_type}</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>200 / 404</t>
+          <t>201 / 404</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
           <t>Generation</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>PATCH</t>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>/api/generate/{job_id}/section/{section_id}</t>
+          <t>/api/generate/{job_id}/section/{section_id}/regenerate</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Manual content override → new version</t>
+          <t>Regenerate a section. NEW: send {"instruction":"..."} to revise it using the user input in ONE call (revision mode). Also accepts {"comment_id"}. Empty body = regenerate from scratch.</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>opt (attribution)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>{content}</t>
+          <t>{instruction? | comment_id?}</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
@@ -1438,7 +1438,7 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
@@ -1452,12 +1452,12 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>/api/generate/{job_id}/section/{section_id}/comment</t>
+          <t>/api/generate/{job_id}/section/{section_id}/accept</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Add an edit-request comment</t>
+          <t>Accept a specific version</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1467,37 +1467,37 @@
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>{comment_text, comment_type}</t>
+          <t>{version_number}</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>201 / 404</t>
+          <t>200 / 404</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
           <t>Generation</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>/api/generate/{job_id}/section/{section_id}/regenerate</t>
+          <t>/api/generate/{job_id}/preview</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Regenerate a section (optionally from comment)</t>
+          <t>Assembled preview (sections + markdown)</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>{comment_id?}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
@@ -1518,26 +1518,26 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
           <t>Generation</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>/api/generate/{job_id}/section/{section_id}/accept</t>
+          <t>/api/generate/{job_id}/preview/html</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Accept a specific version</t>
+          <t>LibreOffice HTML preview (sync)</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1547,18 +1547,18 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>{version_number}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>200 / 404</t>
+          <t>200 / 202 / 404</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>/api/generate/{job_id}/preview</t>
+          <t>/api/generate/{job_id}/stream</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Assembled preview (sections + markdown)</t>
+          <t>Server-Sent Events — live generation progress</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1592,32 +1592,32 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>200 / 404</t>
+          <t>200 text/event-stream</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
           <t>Generation</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>/api/generate/{job_id}/preview/html</t>
+          <t>/api/generate/{job_id}/snapshot</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>LibreOffice HTML preview (sync)</t>
+          <t>Save a version checkpoint</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1627,18 +1627,18 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{label, trigger_type}</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>200 / 202 / 404</t>
+          <t>201 / 404</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
@@ -1652,12 +1652,12 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>/api/generate/{job_id}/preview/status</t>
+          <t>/api/generate/{job_id}/snapshots</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Legacy preview-poll shim</t>
+          <t>List version history</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1667,37 +1667,37 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>?task_id=</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>200 / 202 / 400</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
           <t>Generation</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>/api/generate/{job_id}/stream</t>
+          <t>/api/generate/{job_id}/snapshot/{snapshot_id}/restore</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Server-Sent Events — live generation progress</t>
+          <t>Restore a snapshot</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1712,72 +1712,72 @@
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>200 text/event-stream</t>
+          <t>200 / 404</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
           <t>Generation</t>
         </is>
       </c>
-      <c r="C30" s="13" t="inlineStr">
-        <is>
-          <t>PATCH</t>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>/api/sections/{section_id}</t>
+          <t>/api/generate/{job_id}/validate</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Inline preview-editor save → new version</t>
+          <t>Validation Agent: quality score + source-doc provenance</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>opt (attribution)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>{content}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
-          <t>200 / 404</t>
+          <t>200 / 409 (not done) / 404</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
           <t>Generation</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>/api/generate/{job_id}/snapshot</t>
+          <t>/api/generate/{job_id}/export</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Save a version checkpoint</t>
+          <t>Export document (docx / pdf / md)</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1787,22 +1787,22 @@
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>{label, trigger_type}</t>
+          <t>?format=docx|pdf|md</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>201 / 404</t>
+          <t>200 file/blob / 404</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="12" t="inlineStr">
-        <is>
-          <t>Generation</t>
+        <v>32</v>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>Templates</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>/api/generate/{job_id}/snapshots</t>
+          <t>/api/templates</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>List version history</t>
+          <t>List templates (optionally by doc type)</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>?document_type=</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
@@ -1838,11 +1838,11 @@
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>Generation</t>
+        <v>33</v>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>Templates</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -1852,12 +1852,12 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>/api/generate/{job_id}/snapshot/{snapshot_id}/restore</t>
+          <t>/api/templates</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Restore a snapshot</t>
+          <t>Create a user template</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1867,22 +1867,22 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{name, document_type, sections}</t>
         </is>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>200 / 404</t>
+          <t>201 / 400</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>Generation</t>
+        <v>34</v>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>Templates</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>/api/generate/{job_id}/validate</t>
+          <t>/api/templates/{template_id}/reseed</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Validation Agent: quality score + source-doc provenance</t>
+          <t>Reseed a template from its JSON</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -1912,32 +1912,32 @@
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
-          <t>200 / 409 (not done) / 404</t>
+          <t>200 / 404</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>Generation</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>GET</t>
+        <v>35</v>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>Projects</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>/api/generate/{job_id}/export</t>
+          <t>/api/projects/draft</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Export document (docx / pdf / md)</t>
+          <t>Create / upsert a draft project (idempotent)</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -1947,22 +1947,22 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>?format=docx|pdf|md</t>
+          <t>{project_id?, ...fields}</t>
         </is>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>200 file/blob / 404</t>
+          <t>201 / 200 (exists) / 409 (code)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="14" t="inlineStr">
-        <is>
-          <t>Templates</t>
+        <v>36</v>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>Projects</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -1972,12 +1972,12 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>/api/templates</t>
+          <t>/api/projects/stats</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>List templates (optionally by doc type)</t>
+          <t>Dashboard KPI counts (Total/Draft/Review/Approved)</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>?document_type=</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H36" s="9" t="inlineStr">
@@ -1998,11 +1998,11 @@
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t>Templates</t>
+        <v>37</v>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>Projects</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>/api/templates</t>
+          <t>/api/projects</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>Create a user template</t>
+          <t>Create a fully-validated project (strict)</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -2027,37 +2027,37 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>{name, document_type, sections}</t>
+          <t>ProjectFormData</t>
         </is>
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
-          <t>201 / 400</t>
+          <t>201 / 422 (validation)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="14" t="inlineStr">
-        <is>
-          <t>Templates</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>POST</t>
+        <v>38</v>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>Projects</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>/api/templates/{template_id}/reseed</t>
+          <t>/api/projects</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>Reseed a template from its JSON</t>
+          <t>List projects — search / status / dept / pagination</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -2067,37 +2067,37 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>?q,status,business_unit,review_status,page</t>
         </is>
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
-          <t>200 / 404</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>/api/projects/draft</t>
+          <t>/api/projects/{project_id}/documents</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>Create / upsert a draft project (idempotent)</t>
+          <t>Per-document-type states (multi-doc project)</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -2107,18 +2107,18 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>{project_id?, ...fields}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
-          <t>201 / 200 (exists) / 409 (code)</t>
+          <t>200 / 404</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
@@ -2132,12 +2132,12 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>/api/projects/stats</t>
+          <t>/api/projects/{project_id}/data</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>Dashboard KPI counts (Total/Draft/Review/Approved)</t>
+          <t>Ingested + AI-derived fields</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -2152,32 +2152,32 @@
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>200 / 404</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="C41" s="10" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C41" s="16" t="inlineStr">
+        <is>
+          <t>PUT</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>/api/projects</t>
+          <t>/api/projects/{project_id}/data/ingested</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>Create a fully-validated project (strict)</t>
+          <t>Save edits to ingested fields</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -2187,37 +2187,37 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>ProjectFormData</t>
+          <t>{fields}</t>
         </is>
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
-          <t>201 / 422 (validation)</t>
+          <t>200 / 404 / 409</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>PUT</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>/api/projects</t>
+          <t>/api/projects/{project_id}/data/derived</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>List projects — search / status / dept / pagination</t>
+          <t>Save edits to AI-derived fields</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -2227,37 +2227,37 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>?q,status,business_unit,review_status,page</t>
+          <t>{derived fields}</t>
         </is>
       </c>
       <c r="H42" s="9" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>200 / 404</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>/api/projects/{project_id}/documents</t>
+          <t>/api/projects/{project_id}/derive-fields</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>Per-document-type states (multi-doc project)</t>
+          <t>AI-derive the 12 extended fields</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="H43" s="9" t="inlineStr">
         <is>
-          <t>200 / 404</t>
+          <t>200 / 404 / 502</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>/api/projects/{project_id}/data</t>
+          <t>/api/projects/{project_id}/validate</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>Ingested + AI-derived fields</t>
+          <t>Pre-generation required-field check</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -2318,26 +2318,26 @@
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="C45" s="16" t="inlineStr">
-        <is>
-          <t>PUT</t>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>/api/projects/{project_id}/data/ingested</t>
+          <t>/api/projects/{project_id}</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>Save edits to ingested fields</t>
+          <t>Full project record</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -2347,37 +2347,37 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>{fields}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H45" s="9" t="inlineStr">
         <is>
-          <t>200 / 404 / 409</t>
+          <t>200 / 404</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="C46" s="16" t="inlineStr">
-        <is>
-          <t>PUT</t>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>/api/projects/{project_id}/data/derived</t>
+          <t>/api/projects/{project_id}</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>Save edits to AI-derived fields</t>
+          <t>Partial update / autosave</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -2387,37 +2387,37 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>{derived fields}</t>
+          <t>{fields}</t>
         </is>
       </c>
       <c r="H46" s="9" t="inlineStr">
         <is>
-          <t>200 / 404</t>
+          <t>200 / 400 (empty) / 404</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="C47" s="10" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>/api/projects/{project_id}/derive-fields</t>
+          <t>/api/projects/{project_id}</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>AI-derive the 12 extended fields</t>
+          <t>Delete a project</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -2432,17 +2432,17 @@
       </c>
       <c r="H47" s="9" t="inlineStr">
         <is>
-          <t>200 / 404 / 502</t>
+          <t>204 / 404</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48" s="15" t="inlineStr">
-        <is>
-          <t>Projects</t>
+        <v>49</v>
+      </c>
+      <c r="B48" s="18" t="inlineStr">
+        <is>
+          <t>Chat</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>/api/projects/{project_id}/validate</t>
+          <t>/api/chat/init</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>Pre-generation required-field check</t>
+          <t>Init / resume a chat session (auto-creates draft)</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -2467,37 +2467,37 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{project_id?, document_type, project_name?}</t>
         </is>
       </c>
       <c r="H48" s="9" t="inlineStr">
         <is>
-          <t>200 / 404</t>
+          <t>201</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49" s="15" t="inlineStr">
-        <is>
-          <t>Projects</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>GET</t>
+        <v>50</v>
+      </c>
+      <c r="B49" s="18" t="inlineStr">
+        <is>
+          <t>Chat</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>/api/projects/{project_id}</t>
+          <t>/api/chat/message</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>Full project record</t>
+          <t>Send a chat message</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -2507,37 +2507,37 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{session_id, message, ...}</t>
         </is>
       </c>
       <c r="H49" s="9" t="inlineStr">
         <is>
-          <t>200 / 404</t>
+          <t>200 / 400</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="B50" s="15" t="inlineStr">
-        <is>
-          <t>Projects</t>
-        </is>
-      </c>
-      <c r="C50" s="16" t="inlineStr">
-        <is>
-          <t>PUT</t>
+        <v>51</v>
+      </c>
+      <c r="B50" s="18" t="inlineStr">
+        <is>
+          <t>Chat</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>/api/projects/{project_id}</t>
+          <t>/api/chat/{session_id}/history</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>DEPRECATED full update (use PATCH)</t>
+          <t>Session message history</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>{fields}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H50" s="9" t="inlineStr">
@@ -2558,26 +2558,26 @@
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="B51" s="15" t="inlineStr">
-        <is>
-          <t>Projects</t>
-        </is>
-      </c>
-      <c r="C51" s="13" t="inlineStr">
-        <is>
-          <t>PATCH</t>
+        <v>52</v>
+      </c>
+      <c r="B51" s="18" t="inlineStr">
+        <is>
+          <t>Chat</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>/api/projects/{project_id}</t>
+          <t>/api/chat/{session_id}/upload</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>Partial update / autosave</t>
+          <t>Upload a document into a chat session</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -2587,37 +2587,37 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>{fields}</t>
+          <t>multipart: file</t>
         </is>
       </c>
       <c r="H51" s="9" t="inlineStr">
         <is>
-          <t>200 / 400 (empty) / 404</t>
+          <t>201 / 400</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="B52" s="15" t="inlineStr">
-        <is>
-          <t>Projects</t>
-        </is>
-      </c>
-      <c r="C52" s="17" t="inlineStr">
-        <is>
-          <t>DELETE</t>
+        <v>53</v>
+      </c>
+      <c r="B52" s="19" t="inlineStr">
+        <is>
+          <t>Users</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>/api/projects/{project_id}</t>
+          <t>/api/users</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>Delete a project</t>
+          <t>List users (Admin panel)</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -2632,17 +2632,17 @@
       </c>
       <c r="H52" s="9" t="inlineStr">
         <is>
-          <t>204 / 404</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="B53" s="18" t="inlineStr">
-        <is>
-          <t>Chat</t>
+        <v>54</v>
+      </c>
+      <c r="B53" s="19" t="inlineStr">
+        <is>
+          <t>Users</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>/api/chat/init</t>
+          <t>/api/users</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>Init / resume a chat session (auto-creates draft)</t>
+          <t>Upsert a user</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -2667,37 +2667,37 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>{project_id?, document_type, project_name?}</t>
+          <t>{email, name, role}</t>
         </is>
       </c>
       <c r="H53" s="9" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>201 / 400</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="B54" s="18" t="inlineStr">
-        <is>
-          <t>Chat</t>
-        </is>
-      </c>
-      <c r="C54" s="10" t="inlineStr">
-        <is>
-          <t>POST</t>
+        <v>55</v>
+      </c>
+      <c r="B54" s="19" t="inlineStr">
+        <is>
+          <t>Users</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>/api/chat/message</t>
+          <t>/api/users/{user_id}</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>Send a chat message</t>
+          <t>Delete a user</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -2707,22 +2707,22 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>{session_id, message, ...}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H54" s="9" t="inlineStr">
         <is>
-          <t>200 / 400</t>
+          <t>200 / 404</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="B55" s="18" t="inlineStr">
-        <is>
-          <t>Chat</t>
+        <v>56</v>
+      </c>
+      <c r="B55" s="20" t="inlineStr">
+        <is>
+          <t>Personas</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -2732,17 +2732,17 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>/api/chat/{session_id}/history</t>
+          <t>/api/personas</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>Session message history</t>
+          <t>System + caller's custom personas</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
@@ -2752,17 +2752,17 @@
       </c>
       <c r="H55" s="9" t="inlineStr">
         <is>
-          <t>200 / 404</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="B56" s="18" t="inlineStr">
-        <is>
-          <t>Chat</t>
+        <v>57</v>
+      </c>
+      <c r="B56" s="20" t="inlineStr">
+        <is>
+          <t>Personas</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -2772,22 +2772,22 @@
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>/api/chat/{session_id}/upload</t>
+          <t>/api/personas</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>Upload a document into a chat session</t>
+          <t>Create a custom persona</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>multipart: file</t>
+          <t>{name, description}</t>
         </is>
       </c>
       <c r="H56" s="9" t="inlineStr">
@@ -2798,26 +2798,26 @@
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="B57" s="19" t="inlineStr">
-        <is>
-          <t>Users</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>GET</t>
+        <v>58</v>
+      </c>
+      <c r="B57" s="20" t="inlineStr">
+        <is>
+          <t>Personas</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="inlineStr">
+        <is>
+          <t>PUT</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>/api/users</t>
+          <t>/api/personas/{persona_id}</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>List users (Admin panel)</t>
+          <t>Update a custom persona</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -2827,37 +2827,37 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{name?, description?}</t>
         </is>
       </c>
       <c r="H57" s="9" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>200 / 403 (system) / 404</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="B58" s="19" t="inlineStr">
-        <is>
-          <t>Users</t>
-        </is>
-      </c>
-      <c r="C58" s="10" t="inlineStr">
-        <is>
-          <t>POST</t>
+        <v>59</v>
+      </c>
+      <c r="B58" s="20" t="inlineStr">
+        <is>
+          <t>Personas</t>
+        </is>
+      </c>
+      <c r="C58" s="17" t="inlineStr">
+        <is>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>/api/users</t>
+          <t>/api/personas/{persona_id}</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>Upsert a user</t>
+          <t>Delete a custom persona</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -2867,62 +2867,62 @@
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>{email, name, role}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H58" s="9" t="inlineStr">
         <is>
-          <t>201 / 400</t>
+          <t>200 / 403 (system) / 404</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="B59" s="19" t="inlineStr">
-        <is>
-          <t>Users</t>
-        </is>
-      </c>
-      <c r="C59" s="17" t="inlineStr">
-        <is>
-          <t>DELETE</t>
+        <v>60</v>
+      </c>
+      <c r="B59" s="21" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>/api/users/{user_id}</t>
+          <t>/api/review/share</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>Delete a user</t>
+          <t>Share a document for review</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{job_id, reviewers:[...], message}</t>
         </is>
       </c>
       <c r="H59" s="9" t="inlineStr">
         <is>
-          <t>200 / 404</t>
+          <t>201 / 400 / 404</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="B60" s="20" t="inlineStr">
-        <is>
-          <t>Personas</t>
+        <v>61</v>
+      </c>
+      <c r="B60" s="21" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
@@ -2932,17 +2932,17 @@
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>/api/personas</t>
+          <t>/api/review/sent</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>System + caller's custom personas</t>
+          <t>Reviews I requested</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Yes (req)</t>
         </is>
       </c>
       <c r="G60" s="8" t="inlineStr">
@@ -2952,97 +2952,97 @@
       </c>
       <c r="H60" s="9" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>200 / 400 (no header)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="B61" s="20" t="inlineStr">
-        <is>
-          <t>Personas</t>
-        </is>
-      </c>
-      <c r="C61" s="10" t="inlineStr">
-        <is>
-          <t>POST</t>
+        <v>62</v>
+      </c>
+      <c r="B61" s="21" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>/api/personas</t>
+          <t>/api/review/received</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>Create a custom persona</t>
+          <t>Reviews shared with me</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Yes (req)</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>{name, description}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H61" s="9" t="inlineStr">
         <is>
-          <t>201 / 400</t>
+          <t>200 / 400 (no header)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="B62" s="20" t="inlineStr">
-        <is>
-          <t>Personas</t>
-        </is>
-      </c>
-      <c r="C62" s="16" t="inlineStr">
-        <is>
-          <t>PUT</t>
+        <v>63</v>
+      </c>
+      <c r="B62" s="21" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="C62" s="13" t="inlineStr">
+        <is>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>/api/personas/{persona_id}</t>
+          <t>/api/review/comments/{comment_id}</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>Update a custom persona</t>
+          <t>Edit / resolve a comment</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (edit)</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>{name?, description?}</t>
+          <t>{text?, resolved?}</t>
         </is>
       </c>
       <c r="H62" s="9" t="inlineStr">
         <is>
-          <t>200 / 403 (system) / 404</t>
+          <t>200 / 400</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="B63" s="20" t="inlineStr">
-        <is>
-          <t>Personas</t>
+        <v>64</v>
+      </c>
+      <c r="B63" s="21" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
@@ -3052,17 +3052,17 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>/api/personas/{persona_id}</t>
+          <t>/api/review/comments/{comment_id}</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>Delete a custom persona</t>
+          <t>Delete a comment</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
@@ -3072,13 +3072,13 @@
       </c>
       <c r="H63" s="9" t="inlineStr">
         <is>
-          <t>200 / 403 (system) / 404</t>
+          <t>200 / 403</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B64" s="21" t="inlineStr">
         <is>
@@ -3092,33 +3092,33 @@
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>/api/review/share</t>
+          <t>/api/review/comments/{comment_id}/apply</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>Share a document for review</t>
+          <t>Apply comment → regenerate the section</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>{job_id, reviewers:[...], message}</t>
+          <t>{section_id?}</t>
         </is>
       </c>
       <c r="H64" s="9" t="inlineStr">
         <is>
-          <t>201 / 400 / 404</t>
+          <t>200 / 404</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B65" s="21" t="inlineStr">
         <is>
@@ -3132,17 +3132,17 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>/api/review/sent</t>
+          <t>/api/review/{review_id}</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>Reviews I requested</t>
+          <t>Review workspace (doc + reviewers + comments + summaries)</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Yes (req)</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
@@ -3152,117 +3152,117 @@
       </c>
       <c r="H65" s="9" t="inlineStr">
         <is>
-          <t>200 / 400 (no header)</t>
+          <t>200 / 404</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B66" s="21" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
       </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>/api/review/received</t>
+          <t>/api/review/{review_id}/comments</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>Reviews shared with me</t>
+          <t>Add a comment (optionally threaded / anchored)</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Yes (req)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{text, section_id?, parent_id?}</t>
         </is>
       </c>
       <c r="H66" s="9" t="inlineStr">
         <is>
-          <t>200 / 400 (no header)</t>
+          <t>201 / 400</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B67" s="21" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
       </c>
-      <c r="C67" s="13" t="inlineStr">
-        <is>
-          <t>PATCH</t>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>/api/review/comments/{comment_id}</t>
+          <t>/api/review/{review_id}/respond</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>Edit / resolve a comment</t>
+          <t>Submit verdict (accept / reject / revision)</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Yes (edit)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>{text?, resolved?}</t>
+          <t>{action}</t>
         </is>
       </c>
       <c r="H67" s="9" t="inlineStr">
         <is>
-          <t>200 / 400</t>
+          <t>200 / 400 / 403</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B68" s="21" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
       </c>
-      <c r="C68" s="17" t="inlineStr">
-        <is>
-          <t>DELETE</t>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>/api/review/comments/{comment_id}</t>
+          <t>/api/review/{review_id}/renotify</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>Delete a comment</t>
+          <t>Re-notify pending reviewers (in-app)</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
@@ -3272,13 +3272,13 @@
       </c>
       <c r="H68" s="9" t="inlineStr">
         <is>
-          <t>200 / 403</t>
+          <t>200 / 404</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B69" s="21" t="inlineStr">
         <is>
@@ -3292,12 +3292,12 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>/api/review/comments/{comment_id}/apply</t>
+          <t>/api/review/{review_id}/ai-review</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>Apply comment → regenerate the section</t>
+          <t>AI persona review (summary + section comments)</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -3307,58 +3307,58 @@
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>{section_id?}</t>
+          <t>{persona, instructions?}</t>
         </is>
       </c>
       <c r="H69" s="9" t="inlineStr">
         <is>
-          <t>200 / 404</t>
+          <t>200 / 500</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B70" s="21" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
       </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>/api/review/{review_id}</t>
+          <t>/api/review/{review_id}/ai-review/keep</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>Review workspace (doc + reviewers + comments + summaries)</t>
+          <t>Persist the AI comments the reviewer kept</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{persona, comments:[...]}</t>
         </is>
       </c>
       <c r="H70" s="9" t="inlineStr">
         <is>
-          <t>200 / 404</t>
+          <t>201 / 400</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B71" s="21" t="inlineStr">
         <is>
@@ -3372,117 +3372,117 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>/api/review/{review_id}/comments</t>
+          <t>/api/review/{review_id}/summarize</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>Add a comment (optionally threaded / anchored)</t>
+          <t>Persona-wise feedback summaries (cached)</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>{text, section_id?, parent_id?}</t>
+          <t>{personas?, force?}</t>
         </is>
       </c>
       <c r="H71" s="9" t="inlineStr">
         <is>
-          <t>201 / 400</t>
+          <t>200 / 400</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B72" s="21" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
       </c>
-      <c r="C72" s="10" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>/api/review/{review_id}/respond</t>
+          <t>/api/review/{review_id}/summaries</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>Submit verdict (accept / reject / revision)</t>
+          <t>Cached feedback summaries</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>{action}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H72" s="9" t="inlineStr">
         <is>
-          <t>200 / 400 / 403</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
-        <v>69</v>
-      </c>
-      <c r="B73" s="21" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="C73" s="10" t="inlineStr">
-        <is>
-          <t>POST</t>
+        <v>74</v>
+      </c>
+      <c r="B73" s="22" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>/api/review/{review_id}/renotify</t>
+          <t>/api/notifications</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>Re-notify pending reviewers (in-app)</t>
+          <t>My notifications + unread count</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (req)</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>?unread_only, limit</t>
         </is>
       </c>
       <c r="H73" s="9" t="inlineStr">
         <is>
-          <t>200 / 404</t>
+          <t>200 / 400</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="B74" s="21" t="inlineStr">
-        <is>
-          <t>Review</t>
+        <v>75</v>
+      </c>
+      <c r="B74" s="22" t="inlineStr">
+        <is>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
@@ -3492,227 +3492,101 @@
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>/api/review/{review_id}/ai-review</t>
+          <t>/api/notifications/read</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>AI persona review (summary + section comments)</t>
+          <t>Mark notification(s) read</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (req)</t>
         </is>
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>{persona, instructions?}</t>
+          <t>{ids?:[...]}</t>
         </is>
       </c>
       <c r="H74" s="9" t="inlineStr">
         <is>
-          <t>200 / 500</t>
+          <t>200 / 400</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="n">
-        <v>71</v>
-      </c>
-      <c r="B75" s="21" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="C75" s="10" t="inlineStr">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Generation</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>/api/review/{review_id}/ai-review/keep</t>
-        </is>
-      </c>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t>Persist the AI comments the reviewer kept</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>/api/generate/{job_id}/preview/save</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Manual whole-document HTML edit → stored as a version (author). Live preview then serves it.</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G75" s="8" t="inlineStr">
-        <is>
-          <t>{persona, comments:[...]}</t>
-        </is>
-      </c>
-      <c r="H75" s="9" t="inlineStr">
-        <is>
-          <t>201 / 400</t>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>{html, label?}</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>201 / 404</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="B76" s="21" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="C76" s="10" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D76" s="7" t="inlineStr">
-        <is>
-          <t>/api/review/{review_id}/summarize</t>
-        </is>
-      </c>
-      <c r="E76" s="8" t="inlineStr">
-        <is>
-          <t>Persona-wise feedback summaries (cached)</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G76" s="8" t="inlineStr">
-        <is>
-          <t>{personas?, force?}</t>
-        </is>
-      </c>
-      <c r="H76" s="9" t="inlineStr">
-        <is>
-          <t>200 / 400</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="4" t="n">
-        <v>73</v>
-      </c>
-      <c r="B77" s="21" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Generation</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>/api/review/{review_id}/summaries</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="inlineStr">
-        <is>
-          <t>Cached feedback summaries</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G77" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H77" s="9" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="4" t="n">
-        <v>74</v>
-      </c>
-      <c r="B78" s="22" t="inlineStr">
-        <is>
-          <t>Notifications</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>/api/notifications</t>
-        </is>
-      </c>
-      <c r="E78" s="8" t="inlineStr">
-        <is>
-          <t>My notifications + unread count</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>Yes (req)</t>
-        </is>
-      </c>
-      <c r="G78" s="8" t="inlineStr">
-        <is>
-          <t>?unread_only, limit</t>
-        </is>
-      </c>
-      <c r="H78" s="9" t="inlineStr">
-        <is>
-          <t>200 / 400</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="B79" s="22" t="inlineStr">
-        <is>
-          <t>Notifications</t>
-        </is>
-      </c>
-      <c r="C79" s="10" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>/api/notifications/read</t>
-        </is>
-      </c>
-      <c r="E79" s="8" t="inlineStr">
-        <is>
-          <t>Mark notification(s) read</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>Yes (req)</t>
-        </is>
-      </c>
-      <c r="G79" s="8" t="inlineStr">
-        <is>
-          <t>{ids?:[...]}</t>
-        </is>
-      </c>
-      <c r="H79" s="9" t="inlineStr">
-        <is>
-          <t>200 / 400</t>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>/api/generate/{job_id}/snapshot/{snapshot_id}</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Load one version incl. its html_content (view/restore an old edited-HTML version).</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>path only</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>200 / 404</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4014,6 +3888,54 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Changed 2026-07-16</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Regenerate Section now accepts inline instruction (single-call section edit). Chatbot backend hardened vs SQLite database-locked. knowledge.py (RAG grounding) added, inert until enabled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Removed 2026-07-16</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Deleted 5 endpoints (cleanup): POST /generate/start (dep), PUT /projects/{id} (dep), PATCH /sections/{id} (dup), GET .../preview/status (legacy), POST /submit-inputs (legacy). Frontend removed — API-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Added 2026-07-17</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Manual HTML edit feature: POST /preview/save (stores edited HTML as a versioned snapshot with author), GET /snapshot/{id} (loads a version + html). /preview/html now serves the latest manual HTML until a section is regenerated. New DocumentSnapshot cols: author, html_content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Changed 2026-07-17 (fmt)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LibreOffice REMOVED from backend. Preview + PDF now pure-Python, styled from generation/doc_style.py to match the Word (.docx) download. PDF via xhtml2pdf. Preview identical local==Databricks. No API surface change.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
